--- a/Excel/ConditionalFormatting.xlsx
+++ b/Excel/ConditionalFormatting.xlsx
@@ -8,16 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3099C8E-D9AE-43D6-9AA0-ED58889CA158}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F796A14B-23AE-48F8-84C5-5418F718BBC5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="3" xr2:uid="{B85725BA-C1B2-4ACC-90E2-9A97F9208B1E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="6" xr2:uid="{B85725BA-C1B2-4ACC-90E2-9A97F9208B1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Topic" sheetId="1" r:id="rId1"/>
     <sheet name="Ex 1" sheetId="2" r:id="rId2"/>
     <sheet name="Ex 1.1" sheetId="3" r:id="rId3"/>
     <sheet name="Ex 2" sheetId="4" r:id="rId4"/>
+    <sheet name="Ex 3" sheetId="6" r:id="rId5"/>
+    <sheet name="Ex 4" sheetId="7" r:id="rId6"/>
+    <sheet name="Ex 5" sheetId="8" r:id="rId7"/>
+    <sheet name="Ex 5.1" sheetId="11" r:id="rId8"/>
+    <sheet name="Sheet6" sheetId="10" r:id="rId9"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ex 5'!$F$8:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ex 5.1'!$F$8:$L$20</definedName>
+  </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -28,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
   <si>
     <t>What Is Conditional Formating .?</t>
   </si>
@@ -148,13 +157,133 @@
   </si>
   <si>
     <t>Considering the alphabet case while applying the conditional formating</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Head Counts</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>Commercial</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Human Resource</t>
+  </si>
+  <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>Org. Development</t>
+  </si>
+  <si>
+    <t>Production</t>
+  </si>
+  <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>Safety</t>
+  </si>
+  <si>
+    <t>CTRL + SHIFT + C</t>
+  </si>
+  <si>
+    <t>copy format</t>
+  </si>
+  <si>
+    <t>past format</t>
+  </si>
+  <si>
+    <t>CTRL + SHIFT + V</t>
+  </si>
+  <si>
+    <t>Products</t>
+  </si>
+  <si>
+    <t>TOP</t>
+  </si>
+  <si>
+    <t>BOTTOM</t>
+  </si>
+  <si>
+    <t>ABOVE AVERAGE</t>
+  </si>
+  <si>
+    <t>BELOW AVERAGE</t>
+  </si>
+  <si>
+    <t>Product 1</t>
+  </si>
+  <si>
+    <t>Product 10</t>
+  </si>
+  <si>
+    <t>Product 11</t>
+  </si>
+  <si>
+    <t>Product 12</t>
+  </si>
+  <si>
+    <t>Product 2</t>
+  </si>
+  <si>
+    <t>Product 3</t>
+  </si>
+  <si>
+    <t>Product 4</t>
+  </si>
+  <si>
+    <t>Product 5</t>
+  </si>
+  <si>
+    <t>Product 6</t>
+  </si>
+  <si>
+    <t>Product 7</t>
+  </si>
+  <si>
+    <t>Product 8</t>
+  </si>
+  <si>
+    <t>Product 9</t>
+  </si>
+  <si>
+    <t>TOP AND BOTTOM</t>
+  </si>
+  <si>
+    <t>Top 5 items</t>
+  </si>
+  <si>
+    <t>Bottom 5 items</t>
+  </si>
+  <si>
+    <t>TOP 20%</t>
+  </si>
+  <si>
+    <t>BOTTOM 5%</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,8 +305,16 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -190,8 +327,44 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF06D4EA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0070C0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -214,11 +387,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -232,11 +418,55 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="39">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -245,7 +475,32 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor theme="8"/>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -257,6 +512,271 @@
       </font>
       <fill>
         <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
           <bgColor theme="8"/>
         </patternFill>
       </fill>
@@ -273,6 +793,26 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C5700"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -303,176 +843,73 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C5700"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF0070C0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <u val="none"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF06D4EA"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -814,7 +1251,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816E7EB5-95E2-4C71-8401-74A658B5D609}">
-  <dimension ref="E5:J16"/>
+  <dimension ref="E1:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="30.1796875" customWidth="1"/>
@@ -825,6 +1262,22 @@
     <col min="10" max="10" width="13.26953125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="5:10" x14ac:dyDescent="0.35">
+      <c r="F1" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="2" spans="5:10" x14ac:dyDescent="0.35">
+      <c r="F2" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
     <row r="5" spans="5:10" x14ac:dyDescent="0.35">
       <c r="F5" t="s">
         <v>36</v>
@@ -1052,28 +1505,28 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F7:F16">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="containsText" dxfId="33" priority="1" operator="containsText" text="Kol">
+      <formula>NOT(ISERROR(SEARCH("Kol",F7)))</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="32" priority="2" operator="equal">
       <formula>"Chennai"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="6" operator="equal">
       <formula>"Kolkata"</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="Kol">
-      <formula>NOT(ISERROR(SEARCH("Kol",F7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H7:H16">
-    <cfRule type="cellIs" dxfId="12" priority="5" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="30" priority="5" operator="greaterThan">
       <formula>1000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I7:I16">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="lessThan">
+    <cfRule type="cellIs" dxfId="29" priority="4" operator="lessThan">
       <formula>5</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J7:J16">
-    <cfRule type="cellIs" dxfId="10" priority="3" operator="lessThan">
+    <cfRule type="cellIs" dxfId="28" priority="3" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1084,14 +1537,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59799BD0-F880-452C-B8BC-1F3037026791}">
-  <dimension ref="E4:H14"/>
+  <dimension ref="E4:J14"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="27.36328125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12.7265625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E4" s="5" t="s">
         <v>4</v>
       </c>
@@ -1102,7 +1555,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1110,7 +1563,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E6" s="2" t="s">
         <v>13</v>
       </c>
@@ -1118,7 +1571,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1129,7 +1582,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E8" s="2" t="s">
         <v>19</v>
       </c>
@@ -1137,7 +1590,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E9" s="2" t="s">
         <v>22</v>
       </c>
@@ -1145,7 +1598,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E10" s="2" t="s">
         <v>24</v>
       </c>
@@ -1153,23 +1606,35 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E11" s="2" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E12" s="2" t="s">
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="13" spans="5:8" x14ac:dyDescent="0.35">
+      <c r="I12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E13" s="2" t="s">
         <v>32</v>
       </c>
@@ -1177,7 +1642,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="5:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="5:10" x14ac:dyDescent="0.35">
       <c r="E14" s="2" t="s">
         <v>34</v>
       </c>
@@ -1187,7 +1652,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F5:F14">
-    <cfRule type="expression" dxfId="1" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>EXACT($F5,$H$4)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1197,9 +1662,1401 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09AB320-D50B-41B3-91DB-B379FBB4147B}">
-  <dimension ref="A1"/>
+  <dimension ref="E4:L16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" style="4" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="3">
+        <v>100</v>
+      </c>
+      <c r="G5" s="3">
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <v>100</v>
+      </c>
+      <c r="J5">
+        <v>2500</v>
+      </c>
+      <c r="K5">
+        <v>1250</v>
+      </c>
+      <c r="L5">
+        <v>3750</v>
+      </c>
+    </row>
+    <row r="6" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E6" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1250</v>
+      </c>
+      <c r="G6" s="3">
+        <v>4106</v>
+      </c>
+      <c r="H6">
+        <v>5000</v>
+      </c>
+      <c r="J6" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="8">
+        <v>0.25</v>
+      </c>
+      <c r="L6" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="7" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="3">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="8" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E8" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="3">
+        <v>3750</v>
+      </c>
+      <c r="G8" s="3">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="9" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E9" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G9" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="3">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="3">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="11" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E11" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="3">
+        <v>3033</v>
+      </c>
+      <c r="G11" s="3">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="12" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1769</v>
+      </c>
+      <c r="G12" s="3">
+        <v>1769</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="3">
+        <v>4915</v>
+      </c>
+      <c r="G13" s="3">
+        <v>4915</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="3">
+        <v>4259</v>
+      </c>
+      <c r="G14" s="3">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="15" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E15" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="3">
+        <v>1624</v>
+      </c>
+      <c r="G15" s="3">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="16" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E16" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="3">
+        <v>800</v>
+      </c>
+      <c r="G16" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F16">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FF63C384"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{BFE46026-4B8E-42C1-A4DC-052EEAC8E7A8}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G16">
+    <cfRule type="dataBar" priority="1">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2174B4EF-F9FF-4F41-A4C0-686435C2BFB6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{BFE46026-4B8E-42C1-A4DC-052EEAC8E7A8}">
+            <x14:dataBar minLength="0" maxLength="100" border="1" negativeBarBorderColorSameAsPositive="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:borderColor rgb="FF63C384"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:negativeBorderColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>F5:F16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{2174B4EF-F9FF-4F41-A4C0-686435C2BFB6}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G5:G16</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{12D19BB9-FBED-4F20-86EE-EA3EF4B0EC42}">
+  <dimension ref="E4:L16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="17.54296875" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="15.6328125" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E4" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="9">
+        <v>100</v>
+      </c>
+      <c r="G5" s="9">
+        <v>100</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1250</v>
+      </c>
+      <c r="G6" s="9">
+        <v>4106</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="9">
+        <v>3364</v>
+      </c>
+    </row>
+    <row r="8" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="9">
+        <v>3750</v>
+      </c>
+      <c r="G8" s="9">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="9" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="9">
+        <v>5000</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="9">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="11" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3033</v>
+      </c>
+      <c r="G11" s="9">
+        <v>3033</v>
+      </c>
+    </row>
+    <row r="12" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="9">
+        <v>1769</v>
+      </c>
+      <c r="G12" s="9">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="13" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="9">
+        <v>4915</v>
+      </c>
+      <c r="G13" s="9">
+        <v>4915</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="9">
+        <v>4259</v>
+      </c>
+      <c r="G14" s="9">
+        <v>4259</v>
+      </c>
+    </row>
+    <row r="15" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1624</v>
+      </c>
+      <c r="G15" s="9">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="16" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="9">
+        <v>800</v>
+      </c>
+      <c r="G16" s="9">
+        <v>8000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F16">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G16">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFCFCFF"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04921A2A-477E-4BCE-9DA8-10CD662CB63A}">
+  <dimension ref="E4:L16"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="5" max="5" width="17.54296875" customWidth="1"/>
+    <col min="6" max="6" width="17.453125" customWidth="1"/>
+    <col min="7" max="7" width="15.26953125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="11.7265625" customWidth="1"/>
+    <col min="10" max="10" width="15.6328125" customWidth="1"/>
+    <col min="11" max="11" width="14.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="5:12" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E4" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E5" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="F5" s="9">
+        <v>100</v>
+      </c>
+      <c r="G5" s="9">
+        <v>100</v>
+      </c>
+      <c r="H5" s="3">
+        <v>100</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="6" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E6" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="9">
+        <v>1250</v>
+      </c>
+      <c r="G6" s="9">
+        <v>410</v>
+      </c>
+      <c r="H6" s="3">
+        <v>410</v>
+      </c>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8"/>
+      <c r="L6" s="8"/>
+    </row>
+    <row r="7" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E7" s="9" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" s="9">
+        <v>2500</v>
+      </c>
+      <c r="G7" s="9">
+        <v>336</v>
+      </c>
+      <c r="H7" s="3">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="8" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="9">
+        <v>3750</v>
+      </c>
+      <c r="G8" s="9">
+        <v>2243</v>
+      </c>
+      <c r="H8" s="3">
+        <v>2243</v>
+      </c>
+    </row>
+    <row r="9" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E9" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="F9" s="9">
+        <v>5000</v>
+      </c>
+      <c r="G9" s="9">
+        <v>5000</v>
+      </c>
+      <c r="H9" s="3">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E10" s="9" t="s">
+        <v>47</v>
+      </c>
+      <c r="F10" s="9">
+        <v>2500</v>
+      </c>
+      <c r="G10" s="9">
+        <v>4500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="11" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E11" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="9">
+        <v>3033</v>
+      </c>
+      <c r="G11" s="9">
+        <v>4000</v>
+      </c>
+      <c r="H11" s="3">
+        <v>4000</v>
+      </c>
+    </row>
+    <row r="12" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E12" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="9">
+        <v>1769</v>
+      </c>
+      <c r="G12" s="9">
+        <v>3500</v>
+      </c>
+      <c r="H12" s="3">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="13" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E13" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F13" s="9">
+        <v>4915</v>
+      </c>
+      <c r="G13" s="9">
+        <v>6000</v>
+      </c>
+      <c r="H13" s="3">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="14" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E14" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="9">
+        <v>4259</v>
+      </c>
+      <c r="G14" s="9">
+        <v>6500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>6500</v>
+      </c>
+    </row>
+    <row r="15" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E15" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="9">
+        <v>1624</v>
+      </c>
+      <c r="G15" s="9">
+        <v>7000</v>
+      </c>
+      <c r="H15" s="3">
+        <v>7000</v>
+      </c>
+    </row>
+    <row r="16" spans="5:12" x14ac:dyDescent="0.35">
+      <c r="E16" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="9">
+        <v>800</v>
+      </c>
+      <c r="G16" s="9">
+        <v>8000</v>
+      </c>
+      <c r="H16" s="3">
+        <v>8000</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="F5:F16">
+    <cfRule type="iconSet" priority="3">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G5:G16">
+    <cfRule type="iconSet" priority="2">
+      <iconSet iconSet="3Arrows">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="33"/>
+        <cfvo type="percent" val="67"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H5:H16">
+    <cfRule type="iconSet" priority="1">
+      <iconSet iconSet="4Rating">
+        <cfvo type="percent" val="0"/>
+        <cfvo type="percent" val="25"/>
+        <cfvo type="percent" val="50"/>
+        <cfvo type="percent" val="75"/>
+      </iconSet>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9743B30D-C889-406F-9DE0-A4DF8EFE026F}">
+  <dimension ref="F8:L20"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="4" width="8.7265625" style="13"/>
+    <col min="5" max="5" width="13.1796875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="14" style="13" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="15.08984375" style="13" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="19.54296875" style="13" customWidth="1"/>
+    <col min="11" max="11" width="17.36328125" style="13" customWidth="1"/>
+    <col min="12" max="12" width="14.6328125" style="13" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="8" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="J8" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="L8" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F9" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="9">
+        <v>60</v>
+      </c>
+      <c r="H9" s="9">
+        <v>6</v>
+      </c>
+      <c r="I9" s="9">
+        <v>60</v>
+      </c>
+      <c r="J9" s="9">
+        <v>60</v>
+      </c>
+      <c r="K9" s="9">
+        <v>60</v>
+      </c>
+      <c r="L9" s="9">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F10" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="9">
+        <v>12</v>
+      </c>
+      <c r="H10" s="9">
+        <v>120</v>
+      </c>
+      <c r="I10" s="9">
+        <v>120</v>
+      </c>
+      <c r="J10" s="9">
+        <v>120</v>
+      </c>
+      <c r="K10" s="9">
+        <v>120</v>
+      </c>
+      <c r="L10" s="9">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="11" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F11" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="9">
+        <v>150</v>
+      </c>
+      <c r="H11" s="9">
+        <v>10</v>
+      </c>
+      <c r="I11" s="9">
+        <v>10</v>
+      </c>
+      <c r="J11" s="9">
+        <v>10</v>
+      </c>
+      <c r="K11" s="9">
+        <v>10</v>
+      </c>
+      <c r="L11" s="9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F12" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="9">
+        <v>100</v>
+      </c>
+      <c r="H12" s="9">
+        <v>100</v>
+      </c>
+      <c r="I12" s="9">
+        <v>100</v>
+      </c>
+      <c r="J12" s="9">
+        <v>-90</v>
+      </c>
+      <c r="K12" s="9">
+        <v>100</v>
+      </c>
+      <c r="L12" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F13" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="9">
+        <v>20</v>
+      </c>
+      <c r="H13" s="9">
+        <v>20</v>
+      </c>
+      <c r="I13" s="9">
+        <v>20</v>
+      </c>
+      <c r="J13" s="9">
+        <v>20</v>
+      </c>
+      <c r="K13" s="9">
+        <v>20</v>
+      </c>
+      <c r="L13" s="9">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F14" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="9">
+        <v>40</v>
+      </c>
+      <c r="H14" s="9">
+        <v>40</v>
+      </c>
+      <c r="I14" s="9">
+        <v>40</v>
+      </c>
+      <c r="J14" s="9">
+        <v>40</v>
+      </c>
+      <c r="K14" s="9">
+        <v>40</v>
+      </c>
+      <c r="L14" s="9">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F15" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="9">
+        <v>110</v>
+      </c>
+      <c r="H15" s="9">
+        <v>110</v>
+      </c>
+      <c r="I15" s="9">
+        <v>110</v>
+      </c>
+      <c r="J15" s="9">
+        <v>110</v>
+      </c>
+      <c r="K15" s="9">
+        <v>110</v>
+      </c>
+      <c r="L15" s="9">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="16" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F16" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="9">
+        <v>50</v>
+      </c>
+      <c r="H16" s="9">
+        <v>50</v>
+      </c>
+      <c r="I16" s="9">
+        <v>50</v>
+      </c>
+      <c r="J16" s="9">
+        <v>50</v>
+      </c>
+      <c r="K16" s="9">
+        <v>50</v>
+      </c>
+      <c r="L16" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F17" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="9">
+        <v>70</v>
+      </c>
+      <c r="H17" s="9">
+        <v>70</v>
+      </c>
+      <c r="I17" s="9">
+        <v>70</v>
+      </c>
+      <c r="J17" s="9">
+        <v>70</v>
+      </c>
+      <c r="K17" s="9">
+        <v>70</v>
+      </c>
+      <c r="L17" s="9">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="18" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F18" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="9">
+        <v>90</v>
+      </c>
+      <c r="H18" s="9">
+        <v>90</v>
+      </c>
+      <c r="I18" s="9">
+        <v>90</v>
+      </c>
+      <c r="J18" s="9">
+        <v>90</v>
+      </c>
+      <c r="K18" s="9">
+        <v>90</v>
+      </c>
+      <c r="L18" s="9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F19" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="9">
+        <v>80</v>
+      </c>
+      <c r="H19" s="9">
+        <v>80</v>
+      </c>
+      <c r="I19" s="9">
+        <v>80</v>
+      </c>
+      <c r="J19" s="9">
+        <v>80</v>
+      </c>
+      <c r="K19" s="9">
+        <v>80</v>
+      </c>
+      <c r="L19" s="9">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F20" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="9">
+        <v>30</v>
+      </c>
+      <c r="H20" s="9">
+        <v>30</v>
+      </c>
+      <c r="I20" s="9">
+        <v>30</v>
+      </c>
+      <c r="J20" s="9">
+        <v>30</v>
+      </c>
+      <c r="K20" s="9">
+        <v>30</v>
+      </c>
+      <c r="L20" s="9">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="F9:F20">
+    <sortCondition ref="F9"/>
+  </sortState>
+  <conditionalFormatting sqref="G9:G20">
+    <cfRule type="top10" dxfId="10" priority="6" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H9:H20">
+    <cfRule type="top10" dxfId="9" priority="5" bottom="1" rank="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I9:I20">
+    <cfRule type="aboveAverage" dxfId="8" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9:J20">
+    <cfRule type="aboveAverage" dxfId="7" priority="3" aboveAverage="0"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K9:K20">
+    <cfRule type="top10" dxfId="6" priority="2" percent="1" rank="20"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="L9:L20">
+    <cfRule type="top10" dxfId="0" priority="1" percent="1" bottom="1" rank="5"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFCF6F2-9FA5-4AA7-BF81-75AF25E027BE}">
+  <dimension ref="F1:L32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="4" width="8.7265625" style="13"/>
+    <col min="5" max="5" width="13.1796875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="14" style="13" customWidth="1"/>
+    <col min="7" max="7" width="16.36328125" style="13" customWidth="1"/>
+    <col min="8" max="8" width="12.453125" style="13" customWidth="1"/>
+    <col min="9" max="9" width="17.6328125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="19.54296875" style="13" customWidth="1"/>
+    <col min="11" max="11" width="13.90625" style="13" customWidth="1"/>
+    <col min="12" max="12" width="13.81640625" style="13" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H1"/>
+      <c r="I1"/>
+    </row>
+    <row r="2" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H2"/>
+      <c r="I2"/>
+    </row>
+    <row r="3" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H3"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H4"/>
+      <c r="I4"/>
+    </row>
+    <row r="5" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H5"/>
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H6"/>
+      <c r="I6"/>
+    </row>
+    <row r="7" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="H7"/>
+      <c r="I7"/>
+    </row>
+    <row r="8" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F8" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="H8"/>
+      <c r="I8"/>
+      <c r="J8"/>
+      <c r="K8" s="15"/>
+      <c r="L8" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="9" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F9" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="G9" s="3">
+        <v>60</v>
+      </c>
+      <c r="H9"/>
+      <c r="I9"/>
+      <c r="J9"/>
+      <c r="K9" s="16"/>
+      <c r="L9" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F10" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="3">
+        <v>12</v>
+      </c>
+      <c r="J10"/>
+      <c r="K10"/>
+      <c r="L10"/>
+    </row>
+    <row r="11" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F11" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="G11" s="3">
+        <v>150</v>
+      </c>
+      <c r="J11"/>
+      <c r="K11"/>
+      <c r="L11"/>
+    </row>
+    <row r="12" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F12" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="G12" s="3">
+        <v>100</v>
+      </c>
+      <c r="H12"/>
+      <c r="I12"/>
+      <c r="J12"/>
+      <c r="K12"/>
+      <c r="L12"/>
+    </row>
+    <row r="13" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F13" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="G13" s="3">
+        <v>20</v>
+      </c>
+      <c r="H13"/>
+      <c r="I13"/>
+      <c r="J13"/>
+      <c r="K13"/>
+      <c r="L13"/>
+    </row>
+    <row r="14" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F14" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="G14" s="3">
+        <v>40</v>
+      </c>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="L14"/>
+    </row>
+    <row r="15" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F15" s="14" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="3">
+        <v>110</v>
+      </c>
+      <c r="H15"/>
+      <c r="I15"/>
+      <c r="J15"/>
+      <c r="K15"/>
+      <c r="L15"/>
+    </row>
+    <row r="16" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F16" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="G16" s="3">
+        <v>50</v>
+      </c>
+      <c r="H16"/>
+      <c r="I16"/>
+      <c r="J16"/>
+      <c r="K16"/>
+      <c r="L16"/>
+    </row>
+    <row r="17" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F17" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="3">
+        <v>70</v>
+      </c>
+      <c r="H17"/>
+      <c r="I17"/>
+      <c r="J17"/>
+      <c r="K17"/>
+      <c r="L17"/>
+    </row>
+    <row r="18" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F18" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="G18" s="3">
+        <v>90</v>
+      </c>
+      <c r="H18"/>
+      <c r="I18"/>
+      <c r="J18"/>
+      <c r="K18"/>
+      <c r="L18"/>
+    </row>
+    <row r="19" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F19" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="G19" s="3">
+        <v>80</v>
+      </c>
+      <c r="H19"/>
+      <c r="I19"/>
+      <c r="J19"/>
+      <c r="K19"/>
+      <c r="L19"/>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="F20" s="14" t="s">
+        <v>74</v>
+      </c>
+      <c r="G20" s="3">
+        <v>30</v>
+      </c>
+      <c r="H20"/>
+      <c r="I20"/>
+      <c r="J20"/>
+      <c r="K20"/>
+      <c r="L20"/>
+    </row>
+    <row r="21" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G21" s="3">
+        <v>6</v>
+      </c>
+      <c r="H21"/>
+      <c r="I21"/>
+      <c r="J21"/>
+      <c r="K21"/>
+      <c r="L21"/>
+    </row>
+    <row r="22" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G22" s="3">
+        <v>120</v>
+      </c>
+      <c r="H22"/>
+      <c r="I22"/>
+    </row>
+    <row r="23" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G23" s="3">
+        <v>10</v>
+      </c>
+      <c r="H23"/>
+      <c r="I23"/>
+    </row>
+    <row r="24" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G24" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G25" s="3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G26" s="3">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="27" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G27" s="3">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="28" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G28" s="3">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G29" s="3">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="30" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G30" s="3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G31" s="3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="32" spans="6:12" x14ac:dyDescent="0.35">
+      <c r="G32" s="3">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="G9:G32">
+    <cfRule type="top10" dxfId="26" priority="1" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="25" priority="2" rank="5"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61830D79-1D6E-43CC-B91F-35DAFBD54708}">
+  <dimension ref="A1:A12"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>120</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A1:A12">
+    <sortCondition ref="A1"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Excel/ConditionalFormatting.xlsx
+++ b/Excel/ConditionalFormatting.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F796A14B-23AE-48F8-84C5-5418F718BBC5}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A50D72D3-6211-4B74-B29D-90C5B3D8EA52}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="6" xr2:uid="{B85725BA-C1B2-4ACC-90E2-9A97F9208B1E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" firstSheet="2" activeTab="11" xr2:uid="{B85725BA-C1B2-4ACC-90E2-9A97F9208B1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Topic" sheetId="1" r:id="rId1"/>
@@ -21,11 +21,18 @@
     <sheet name="Ex 4" sheetId="7" r:id="rId6"/>
     <sheet name="Ex 5" sheetId="8" r:id="rId7"/>
     <sheet name="Ex 5.1" sheetId="11" r:id="rId8"/>
-    <sheet name="Sheet6" sheetId="10" r:id="rId9"/>
+    <sheet name="Ex 6Cust1" sheetId="12" r:id="rId9"/>
+    <sheet name="Ex 6Cust2" sheetId="15" r:id="rId10"/>
+    <sheet name="Ex 6Cust3" sheetId="16" r:id="rId11"/>
+    <sheet name="Ex 6Cust4" sheetId="17" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Ex 5'!$F$8:$L$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Ex 5.1'!$F$8:$L$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Ex 6Cust1'!$A$2:$D$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Ex 6Cust2'!$A$2:$D$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Ex 6Cust3'!$A$2:$D$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Ex 6Cust4'!$A$2:$D$98</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
   <extLst>
@@ -37,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="962" uniqueCount="186">
   <si>
     <t>What Is Conditional Formating .?</t>
   </si>
@@ -277,6 +284,324 @@
   </si>
   <si>
     <t>BOTTOM 5%</t>
+  </si>
+  <si>
+    <t>Emp Name</t>
+  </si>
+  <si>
+    <t>Dt. Of Joining</t>
+  </si>
+  <si>
+    <t>Salary</t>
+  </si>
+  <si>
+    <t>Ahlam Aby</t>
+  </si>
+  <si>
+    <t>Accounting</t>
+  </si>
+  <si>
+    <t>Alicia A. Elmasian</t>
+  </si>
+  <si>
+    <t>Alison Johnson</t>
+  </si>
+  <si>
+    <t>Customer Support</t>
+  </si>
+  <si>
+    <t>Alyssa Adefioye</t>
+  </si>
+  <si>
+    <t>Ann Sharp</t>
+  </si>
+  <si>
+    <t>Benny Erwin</t>
+  </si>
+  <si>
+    <t>Benny Melendez</t>
+  </si>
+  <si>
+    <t>Human Resources</t>
+  </si>
+  <si>
+    <t>Brian M Stucki</t>
+  </si>
+  <si>
+    <t>Brian Tomasevic</t>
+  </si>
+  <si>
+    <t>Bryan Anderson</t>
+  </si>
+  <si>
+    <t>Bryan Brier</t>
+  </si>
+  <si>
+    <t>Cassandra Perry</t>
+  </si>
+  <si>
+    <t>Christopher Battah</t>
+  </si>
+  <si>
+    <t>Cindy Summerville</t>
+  </si>
+  <si>
+    <t>Corine M. Henderson</t>
+  </si>
+  <si>
+    <t>Cristhian Roth</t>
+  </si>
+  <si>
+    <t>Donna K. Bulgar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elena Miriam Hillen </t>
+  </si>
+  <si>
+    <t>Elena Miriam Takahashi</t>
+  </si>
+  <si>
+    <t>Elena Miriam Woodburn</t>
+  </si>
+  <si>
+    <t>Eric W. Kilbride</t>
+  </si>
+  <si>
+    <t>Erik G. Rinehart</t>
+  </si>
+  <si>
+    <t>Ernest Talia</t>
+  </si>
+  <si>
+    <t>Ernest Trent</t>
+  </si>
+  <si>
+    <t>Gabriel R. Self</t>
+  </si>
+  <si>
+    <t>Genevieve   Knapp</t>
+  </si>
+  <si>
+    <t>Grant Tomasevic</t>
+  </si>
+  <si>
+    <t>Harman Abraha</t>
+  </si>
+  <si>
+    <t>Heela Kraft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ian Helmer </t>
+  </si>
+  <si>
+    <t>Jacqueline N. Gappy</t>
+  </si>
+  <si>
+    <t>Jacqueline N. Hildebrand</t>
+  </si>
+  <si>
+    <t>James Oberndorfer</t>
+  </si>
+  <si>
+    <t>James Wilson</t>
+  </si>
+  <si>
+    <t>Janalee Eggleston</t>
+  </si>
+  <si>
+    <t>Administration</t>
+  </si>
+  <si>
+    <t>Jena Coon</t>
+  </si>
+  <si>
+    <t>Jeremiah De Grazia</t>
+  </si>
+  <si>
+    <t>Jesse Wooten</t>
+  </si>
+  <si>
+    <t>Jessica Rodriguez</t>
+  </si>
+  <si>
+    <t>Joeanne Melendez</t>
+  </si>
+  <si>
+    <t>John  Michael</t>
+  </si>
+  <si>
+    <t>Johnathan A Wilhite</t>
+  </si>
+  <si>
+    <t>Jonathan C. Parnell</t>
+  </si>
+  <si>
+    <t>Joshua Daniel</t>
+  </si>
+  <si>
+    <t>Joshua Fields</t>
+  </si>
+  <si>
+    <t>Joshua Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Julia  Hegwood </t>
+  </si>
+  <si>
+    <t>Julie Harken</t>
+  </si>
+  <si>
+    <t>Julie Yost</t>
+  </si>
+  <si>
+    <t>Katherine Battah</t>
+  </si>
+  <si>
+    <t>Kelley Reneau</t>
+  </si>
+  <si>
+    <t>Kelly Queen</t>
+  </si>
+  <si>
+    <t>Kevin Nevandro</t>
+  </si>
+  <si>
+    <t>Krisaundra Hightower</t>
+  </si>
+  <si>
+    <t>Laura Aguirre</t>
+  </si>
+  <si>
+    <t>Laura S Greenwell</t>
+  </si>
+  <si>
+    <t>Manuel Steele</t>
+  </si>
+  <si>
+    <t>Margaret Pavlovich</t>
+  </si>
+  <si>
+    <t>Martie Elmasian</t>
+  </si>
+  <si>
+    <t>Marylou M. Diaz</t>
+  </si>
+  <si>
+    <t>Matthew H. Rios</t>
+  </si>
+  <si>
+    <t>Matthew Tait</t>
+  </si>
+  <si>
+    <t>Matthew W Yamaguchi</t>
+  </si>
+  <si>
+    <t>Melissa Torruella</t>
+  </si>
+  <si>
+    <t>Micah Chokeir</t>
+  </si>
+  <si>
+    <t>Micah Talia</t>
+  </si>
+  <si>
+    <t>Michelle  Greenwell</t>
+  </si>
+  <si>
+    <t>Michelle  Shevlin</t>
+  </si>
+  <si>
+    <t>Moriel Caldwell</t>
+  </si>
+  <si>
+    <t>Natalie H. Woodford</t>
+  </si>
+  <si>
+    <t>Natalie H. Zeidell</t>
+  </si>
+  <si>
+    <t>Pavan Lalwani</t>
+  </si>
+  <si>
+    <t>Rebecca L. Haight</t>
+  </si>
+  <si>
+    <t>Rebecca Negrete</t>
+  </si>
+  <si>
+    <t>Ricardo Bergman</t>
+  </si>
+  <si>
+    <t>Ricardo Sherrell</t>
+  </si>
+  <si>
+    <t>Richard  Garza</t>
+  </si>
+  <si>
+    <t>Rikkie J Mahone</t>
+  </si>
+  <si>
+    <t>Rosa I. Peralta</t>
+  </si>
+  <si>
+    <t>Rose Moreno</t>
+  </si>
+  <si>
+    <t>Roshan Coon</t>
+  </si>
+  <si>
+    <t>Ryan  Mesko</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryan Kennedy </t>
+  </si>
+  <si>
+    <t>Saif Perrine</t>
+  </si>
+  <si>
+    <t>Sara Webb</t>
+  </si>
+  <si>
+    <t>Saxton Peterson</t>
+  </si>
+  <si>
+    <t>Shireen Battah</t>
+  </si>
+  <si>
+    <t>Stacy L Chen</t>
+  </si>
+  <si>
+    <t>Stephen H. Thomas</t>
+  </si>
+  <si>
+    <t>Steven  Bolin</t>
+  </si>
+  <si>
+    <t>Tamara Pacheco</t>
+  </si>
+  <si>
+    <t>Tiffany M Blake</t>
+  </si>
+  <si>
+    <t>Tony Merrick</t>
+  </si>
+  <si>
+    <t>William Melendez</t>
+  </si>
+  <si>
+    <t>Willow Nevandro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yvette Hurtado </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Max Salary</t>
+  </si>
+  <si>
+    <t>Min Salary</t>
   </si>
 </sst>
 </file>
@@ -404,7 +729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -440,11 +765,246 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="39">
+  <dxfs count="34">
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="8"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color auto="1"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="6" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -488,235 +1048,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -838,68 +1169,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF0070C0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <u val="none"/>
-        <color auto="1"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1249,6 +1518,4217 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A252C84-02AF-413E-921F-1B8B6A8EDB15}">
+  <dimension ref="A2:H98"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="25" style="19" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="4"/>
+    <col min="7" max="7" width="17.81640625" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3">
+        <v>43290</v>
+      </c>
+      <c r="D3" s="3">
+        <v>33869</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="3">
+        <v>43125</v>
+      </c>
+      <c r="D4" s="3">
+        <v>32686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="3">
+        <v>40311</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="3">
+        <v>42777</v>
+      </c>
+      <c r="D6" s="3">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="3">
+        <v>42402</v>
+      </c>
+      <c r="D7" s="3">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3">
+        <v>44168</v>
+      </c>
+      <c r="D8" s="3">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="3">
+        <v>43371</v>
+      </c>
+      <c r="D9" s="3">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="3">
+        <v>40673</v>
+      </c>
+      <c r="D10" s="3">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="3">
+        <v>43403</v>
+      </c>
+      <c r="D11" s="3">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3">
+        <v>40822</v>
+      </c>
+      <c r="D12" s="3">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="3">
+        <v>43678</v>
+      </c>
+      <c r="D13" s="3">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="3">
+        <v>43623</v>
+      </c>
+      <c r="D14" s="3">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3">
+        <v>43233</v>
+      </c>
+      <c r="D15" s="3">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="3">
+        <v>40717</v>
+      </c>
+      <c r="D16" s="3">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>40397</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="3">
+        <v>40635</v>
+      </c>
+      <c r="D18" s="3">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="3">
+        <v>42970</v>
+      </c>
+      <c r="D19" s="3">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3">
+        <v>40838</v>
+      </c>
+      <c r="D20" s="3">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="3">
+        <v>42496</v>
+      </c>
+      <c r="D21" s="3">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="3">
+        <v>42072</v>
+      </c>
+      <c r="D22" s="3">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="3">
+        <v>42272</v>
+      </c>
+      <c r="D23" s="3">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="3">
+        <v>44139</v>
+      </c>
+      <c r="D24" s="3">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="3">
+        <v>43358</v>
+      </c>
+      <c r="D25" s="3">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="3">
+        <v>42911</v>
+      </c>
+      <c r="D26" s="3">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="3">
+        <v>44235</v>
+      </c>
+      <c r="D27" s="3">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="3">
+        <v>42462</v>
+      </c>
+      <c r="D28" s="3">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="3">
+        <v>43129</v>
+      </c>
+      <c r="D29" s="3">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="3">
+        <v>44033</v>
+      </c>
+      <c r="D30" s="3">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="3">
+        <v>43442</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="3">
+        <v>43447</v>
+      </c>
+      <c r="D32" s="3">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="3">
+        <v>43980</v>
+      </c>
+      <c r="D33" s="3">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="3">
+        <v>42593</v>
+      </c>
+      <c r="D34" s="3">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="3">
+        <v>43216</v>
+      </c>
+      <c r="D35" s="3">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="3">
+        <v>44199</v>
+      </c>
+      <c r="D36" s="3">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="3">
+        <v>40837</v>
+      </c>
+      <c r="D37" s="3">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="3">
+        <v>42914</v>
+      </c>
+      <c r="D38" s="3">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="3">
+        <v>40429</v>
+      </c>
+      <c r="D39" s="3">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D40" s="3">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="3">
+        <v>43160</v>
+      </c>
+      <c r="D41" s="3">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="3">
+        <v>40667</v>
+      </c>
+      <c r="D42" s="3">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="3">
+        <v>42813</v>
+      </c>
+      <c r="D43" s="3">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="3">
+        <v>43624</v>
+      </c>
+      <c r="D44" s="3">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D45" s="3">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="3">
+        <v>43912</v>
+      </c>
+      <c r="D46" s="3">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="3">
+        <v>43053</v>
+      </c>
+      <c r="D47" s="3">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="3">
+        <v>42615</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="3">
+        <v>40414</v>
+      </c>
+      <c r="D49" s="3">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D50" s="3">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="3">
+        <v>44142</v>
+      </c>
+      <c r="D51" s="3">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="3">
+        <v>42067</v>
+      </c>
+      <c r="D52" s="3">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="3">
+        <v>42378</v>
+      </c>
+      <c r="D53" s="3">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="3">
+        <v>40556</v>
+      </c>
+      <c r="D54" s="3">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="3">
+        <v>42954</v>
+      </c>
+      <c r="D55" s="3">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="3">
+        <v>42129</v>
+      </c>
+      <c r="D56" s="3">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="3">
+        <v>42220</v>
+      </c>
+      <c r="D57" s="3">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="3">
+        <v>42477</v>
+      </c>
+      <c r="D58" s="3">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="3">
+        <v>44382</v>
+      </c>
+      <c r="D59" s="3">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="3">
+        <v>42936</v>
+      </c>
+      <c r="D60" s="3">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="3">
+        <v>40519</v>
+      </c>
+      <c r="D61" s="3">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="3">
+        <v>42841</v>
+      </c>
+      <c r="D62" s="3">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="3">
+        <v>42995</v>
+      </c>
+      <c r="D63" s="3">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="3">
+        <v>44243</v>
+      </c>
+      <c r="D64" s="3">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="3">
+        <v>42144</v>
+      </c>
+      <c r="D65" s="3">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="3">
+        <v>42296</v>
+      </c>
+      <c r="D66" s="3">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D67" s="3">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="3">
+        <v>43791</v>
+      </c>
+      <c r="D68" s="3">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="3">
+        <v>44131</v>
+      </c>
+      <c r="D69" s="3">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="3">
+        <v>42428</v>
+      </c>
+      <c r="D70" s="3">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="3">
+        <v>42690</v>
+      </c>
+      <c r="D71" s="3">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="3">
+        <v>42359</v>
+      </c>
+      <c r="D72" s="3">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="3">
+        <v>40840</v>
+      </c>
+      <c r="D73" s="3">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="3">
+        <v>40880</v>
+      </c>
+      <c r="D74" s="3">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="3">
+        <v>42049</v>
+      </c>
+      <c r="D75" s="3">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="3">
+        <v>43582</v>
+      </c>
+      <c r="D76" s="3">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" s="3">
+        <v>43034</v>
+      </c>
+      <c r="D77" s="3">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="3">
+        <v>43060</v>
+      </c>
+      <c r="D78" s="3">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" s="3">
+        <v>43846</v>
+      </c>
+      <c r="D79" s="3">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="3">
+        <v>44162</v>
+      </c>
+      <c r="D80" s="3">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C81" s="3">
+        <v>43788</v>
+      </c>
+      <c r="D81" s="3">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="3">
+        <v>42864</v>
+      </c>
+      <c r="D82" s="3">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="3">
+        <v>42856</v>
+      </c>
+      <c r="D83" s="3">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="3">
+        <v>44122</v>
+      </c>
+      <c r="D84" s="3">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="3">
+        <v>40901</v>
+      </c>
+      <c r="D85" s="3">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="3">
+        <v>42430</v>
+      </c>
+      <c r="D86" s="3">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" s="3">
+        <v>43017</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" s="3">
+        <v>43174</v>
+      </c>
+      <c r="D88" s="3">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="3">
+        <v>43951</v>
+      </c>
+      <c r="D89" s="3">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" s="3">
+        <v>40870</v>
+      </c>
+      <c r="D90" s="3">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C91" s="3">
+        <v>42726</v>
+      </c>
+      <c r="D91" s="3">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="3">
+        <v>44229</v>
+      </c>
+      <c r="D92" s="3">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="3">
+        <v>42088</v>
+      </c>
+      <c r="D93" s="3">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" s="3">
+        <v>43218</v>
+      </c>
+      <c r="D94" s="3">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="3">
+        <v>40804</v>
+      </c>
+      <c r="D95" s="3">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C96" s="3">
+        <v>43609</v>
+      </c>
+      <c r="D96" s="3">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" s="3">
+        <v>40469</v>
+      </c>
+      <c r="D97" s="3">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C98" s="3">
+        <v>44179</v>
+      </c>
+      <c r="D98" s="3">
+        <v>30335</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D98" xr:uid="{00E6E89A-8580-41A2-802A-D3ACDA8E2666}"/>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="expression" dxfId="11" priority="4">
+      <formula>$A3=$G$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:A98 C3:C98">
+    <cfRule type="expression" dxfId="10" priority="3">
+      <formula>$A3=$G$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B98">
+    <cfRule type="expression" dxfId="9" priority="2">
+      <formula>$A3=$G$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B3:B98">
+    <cfRule type="expression" dxfId="8" priority="1">
+      <formula>$A3=$G$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8618B15-716E-48C5-80FA-61DFFE6A8F76}">
+  <dimension ref="A2:H98"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="25" style="19" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="4"/>
+    <col min="7" max="7" width="17.81640625" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3">
+        <v>43290</v>
+      </c>
+      <c r="D3" s="3">
+        <v>33869</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="3">
+        <v>30000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="3">
+        <v>43125</v>
+      </c>
+      <c r="D4" s="3">
+        <v>32686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="3">
+        <v>40311</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="3">
+        <v>42777</v>
+      </c>
+      <c r="D6" s="3">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="3">
+        <v>42402</v>
+      </c>
+      <c r="D7" s="3">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="3">
+        <v>44168</v>
+      </c>
+      <c r="D8" s="3">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="3">
+        <v>43371</v>
+      </c>
+      <c r="D9" s="3">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="3">
+        <v>40673</v>
+      </c>
+      <c r="D10" s="3">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="3">
+        <v>43403</v>
+      </c>
+      <c r="D11" s="3">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3">
+        <v>40822</v>
+      </c>
+      <c r="D12" s="3">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="3">
+        <v>43678</v>
+      </c>
+      <c r="D13" s="3">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="3">
+        <v>43623</v>
+      </c>
+      <c r="D14" s="3">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3">
+        <v>43233</v>
+      </c>
+      <c r="D15" s="3">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="3">
+        <v>40717</v>
+      </c>
+      <c r="D16" s="3">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C17" s="3">
+        <v>40397</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="3">
+        <v>40635</v>
+      </c>
+      <c r="D18" s="3">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="3">
+        <v>42970</v>
+      </c>
+      <c r="D19" s="3">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3">
+        <v>40838</v>
+      </c>
+      <c r="D20" s="3">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="3">
+        <v>42496</v>
+      </c>
+      <c r="D21" s="3">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="3">
+        <v>42072</v>
+      </c>
+      <c r="D22" s="3">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="3">
+        <v>42272</v>
+      </c>
+      <c r="D23" s="3">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="3">
+        <v>44139</v>
+      </c>
+      <c r="D24" s="3">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="3">
+        <v>43358</v>
+      </c>
+      <c r="D25" s="3">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="3">
+        <v>42911</v>
+      </c>
+      <c r="D26" s="3">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C27" s="3">
+        <v>44235</v>
+      </c>
+      <c r="D27" s="3">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="3">
+        <v>42462</v>
+      </c>
+      <c r="D28" s="3">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="3">
+        <v>43129</v>
+      </c>
+      <c r="D29" s="3">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="3">
+        <v>44033</v>
+      </c>
+      <c r="D30" s="3">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="3">
+        <v>43442</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="3">
+        <v>43447</v>
+      </c>
+      <c r="D32" s="3">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="3">
+        <v>43980</v>
+      </c>
+      <c r="D33" s="3">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="3">
+        <v>42593</v>
+      </c>
+      <c r="D34" s="3">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="3">
+        <v>43216</v>
+      </c>
+      <c r="D35" s="3">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="3">
+        <v>44199</v>
+      </c>
+      <c r="D36" s="3">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C37" s="3">
+        <v>40837</v>
+      </c>
+      <c r="D37" s="3">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="3">
+        <v>42914</v>
+      </c>
+      <c r="D38" s="3">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="3">
+        <v>40429</v>
+      </c>
+      <c r="D39" s="3">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D40" s="3">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="3">
+        <v>43160</v>
+      </c>
+      <c r="D41" s="3">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="3">
+        <v>40667</v>
+      </c>
+      <c r="D42" s="3">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="3">
+        <v>42813</v>
+      </c>
+      <c r="D43" s="3">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="3">
+        <v>43624</v>
+      </c>
+      <c r="D44" s="3">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D45" s="3">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="3">
+        <v>43912</v>
+      </c>
+      <c r="D46" s="3">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="3">
+        <v>43053</v>
+      </c>
+      <c r="D47" s="3">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="3">
+        <v>42615</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="3">
+        <v>40414</v>
+      </c>
+      <c r="D49" s="3">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D50" s="3">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="3">
+        <v>44142</v>
+      </c>
+      <c r="D51" s="3">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="3">
+        <v>42067</v>
+      </c>
+      <c r="D52" s="3">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="3">
+        <v>42378</v>
+      </c>
+      <c r="D53" s="3">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="3">
+        <v>40556</v>
+      </c>
+      <c r="D54" s="3">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="3">
+        <v>42954</v>
+      </c>
+      <c r="D55" s="3">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="3">
+        <v>42129</v>
+      </c>
+      <c r="D56" s="3">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="3">
+        <v>42220</v>
+      </c>
+      <c r="D57" s="3">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="3">
+        <v>42477</v>
+      </c>
+      <c r="D58" s="3">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="3">
+        <v>44382</v>
+      </c>
+      <c r="D59" s="3">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="3">
+        <v>42936</v>
+      </c>
+      <c r="D60" s="3">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="3">
+        <v>40519</v>
+      </c>
+      <c r="D61" s="3">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="3">
+        <v>42841</v>
+      </c>
+      <c r="D62" s="3">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="3">
+        <v>42995</v>
+      </c>
+      <c r="D63" s="3">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="3">
+        <v>44243</v>
+      </c>
+      <c r="D64" s="3">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="3">
+        <v>42144</v>
+      </c>
+      <c r="D65" s="3">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="3">
+        <v>42296</v>
+      </c>
+      <c r="D66" s="3">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D67" s="3">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="3">
+        <v>43791</v>
+      </c>
+      <c r="D68" s="3">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="3">
+        <v>44131</v>
+      </c>
+      <c r="D69" s="3">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="3">
+        <v>42428</v>
+      </c>
+      <c r="D70" s="3">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="3">
+        <v>42690</v>
+      </c>
+      <c r="D71" s="3">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="3">
+        <v>42359</v>
+      </c>
+      <c r="D72" s="3">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="3">
+        <v>40840</v>
+      </c>
+      <c r="D73" s="3">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="3">
+        <v>40880</v>
+      </c>
+      <c r="D74" s="3">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="3">
+        <v>42049</v>
+      </c>
+      <c r="D75" s="3">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="3">
+        <v>43582</v>
+      </c>
+      <c r="D76" s="3">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" s="3">
+        <v>43034</v>
+      </c>
+      <c r="D77" s="3">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="3">
+        <v>43060</v>
+      </c>
+      <c r="D78" s="3">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" s="3">
+        <v>43846</v>
+      </c>
+      <c r="D79" s="3">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="3">
+        <v>44162</v>
+      </c>
+      <c r="D80" s="3">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C81" s="3">
+        <v>43788</v>
+      </c>
+      <c r="D81" s="3">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="3">
+        <v>42864</v>
+      </c>
+      <c r="D82" s="3">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="3">
+        <v>42856</v>
+      </c>
+      <c r="D83" s="3">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="3">
+        <v>44122</v>
+      </c>
+      <c r="D84" s="3">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="3">
+        <v>40901</v>
+      </c>
+      <c r="D85" s="3">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="3">
+        <v>42430</v>
+      </c>
+      <c r="D86" s="3">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" s="3">
+        <v>43017</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" s="3">
+        <v>43174</v>
+      </c>
+      <c r="D88" s="3">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="3">
+        <v>43951</v>
+      </c>
+      <c r="D89" s="3">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" s="3">
+        <v>40870</v>
+      </c>
+      <c r="D90" s="3">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C91" s="3">
+        <v>42726</v>
+      </c>
+      <c r="D91" s="3">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="3">
+        <v>44229</v>
+      </c>
+      <c r="D92" s="3">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="3">
+        <v>42088</v>
+      </c>
+      <c r="D93" s="3">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" s="3">
+        <v>43218</v>
+      </c>
+      <c r="D94" s="3">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="3">
+        <v>40804</v>
+      </c>
+      <c r="D95" s="3">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C96" s="3">
+        <v>43609</v>
+      </c>
+      <c r="D96" s="3">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" s="3">
+        <v>40469</v>
+      </c>
+      <c r="D97" s="3">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C98" s="3">
+        <v>44179</v>
+      </c>
+      <c r="D98" s="3">
+        <v>30335</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="A3:D98">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>AND($A3=$G$3,$D3&gt;$H$3)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63046BBB-30E1-4C29-9233-5CCC65D05687}">
+  <dimension ref="A2:I98"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="25" style="19" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="4"/>
+    <col min="7" max="7" width="17.81640625" style="4" customWidth="1"/>
+    <col min="8" max="8" width="14.453125" style="4" customWidth="1"/>
+    <col min="9" max="9" width="13.1796875" style="4" customWidth="1"/>
+    <col min="10" max="16384" width="8.7265625" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="3">
+        <v>43125</v>
+      </c>
+      <c r="D3" s="3">
+        <v>3268</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="H3" s="3">
+        <v>20000</v>
+      </c>
+      <c r="I3" s="3">
+        <v>40000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="3">
+        <v>44168</v>
+      </c>
+      <c r="D4" s="3">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C5" s="3">
+        <v>43403</v>
+      </c>
+      <c r="D5" s="3">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>100</v>
+      </c>
+      <c r="C6" s="3">
+        <v>40397</v>
+      </c>
+      <c r="D6" s="3">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="3">
+        <v>42970</v>
+      </c>
+      <c r="D7" s="3">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="3">
+        <v>42272</v>
+      </c>
+      <c r="D8" s="3">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C9" s="3">
+        <v>43442</v>
+      </c>
+      <c r="D9" s="3">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C10" s="3">
+        <v>42813</v>
+      </c>
+      <c r="D10" s="3">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="3">
+        <v>42954</v>
+      </c>
+      <c r="D11" s="3">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C12" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D12" s="3">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C13" s="3">
+        <v>43060</v>
+      </c>
+      <c r="D13" s="3">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="3">
+        <v>44179</v>
+      </c>
+      <c r="D14" s="3">
+        <v>30335</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="3">
+        <v>42914</v>
+      </c>
+      <c r="D15" s="3">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C16" s="3">
+        <v>43160</v>
+      </c>
+      <c r="D16" s="3">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C17" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D17" s="3">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="3">
+        <v>42129</v>
+      </c>
+      <c r="D18" s="3">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" s="3">
+        <v>42477</v>
+      </c>
+      <c r="D19" s="3">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="3">
+        <v>44382</v>
+      </c>
+      <c r="D20" s="3">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C21" s="3">
+        <v>43846</v>
+      </c>
+      <c r="D21" s="3">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C22" s="3">
+        <v>43788</v>
+      </c>
+      <c r="D22" s="3">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C23" s="3">
+        <v>40901</v>
+      </c>
+      <c r="D23" s="3">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C24" s="3">
+        <v>43017</v>
+      </c>
+      <c r="D24" s="3">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="3">
+        <v>43951</v>
+      </c>
+      <c r="D25" s="3">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C26" s="3">
+        <v>44229</v>
+      </c>
+      <c r="D26" s="3">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="3">
+        <v>42777</v>
+      </c>
+      <c r="D27" s="3">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C28" s="3">
+        <v>43129</v>
+      </c>
+      <c r="D28" s="3">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C29" s="3">
+        <v>43980</v>
+      </c>
+      <c r="D29" s="3">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C30" s="3">
+        <v>40837</v>
+      </c>
+      <c r="D30" s="3">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C31" s="3">
+        <v>42067</v>
+      </c>
+      <c r="D31" s="3">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C32" s="3">
+        <v>42296</v>
+      </c>
+      <c r="D32" s="3">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C33" s="3">
+        <v>43791</v>
+      </c>
+      <c r="D33" s="3">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C34" s="3">
+        <v>44131</v>
+      </c>
+      <c r="D34" s="3">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C35" s="3">
+        <v>42428</v>
+      </c>
+      <c r="D35" s="3">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C36" s="3">
+        <v>44122</v>
+      </c>
+      <c r="D36" s="3">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C37" s="3">
+        <v>43609</v>
+      </c>
+      <c r="D37" s="3">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C38" s="3">
+        <v>40469</v>
+      </c>
+      <c r="D38" s="3">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C39" s="3">
+        <v>40311</v>
+      </c>
+      <c r="D39" s="3">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="3">
+        <v>43371</v>
+      </c>
+      <c r="D40" s="3">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="3">
+        <v>43678</v>
+      </c>
+      <c r="D41" s="3">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="3">
+        <v>43623</v>
+      </c>
+      <c r="D42" s="3">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C43" s="3">
+        <v>44139</v>
+      </c>
+      <c r="D43" s="3">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C44" s="3">
+        <v>43447</v>
+      </c>
+      <c r="D44" s="3">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C45" s="3">
+        <v>43216</v>
+      </c>
+      <c r="D45" s="3">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C46" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D46" s="3">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C47" s="3">
+        <v>44142</v>
+      </c>
+      <c r="D47" s="3">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C48" s="3">
+        <v>42378</v>
+      </c>
+      <c r="D48" s="3">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C49" s="3">
+        <v>40556</v>
+      </c>
+      <c r="D49" s="3">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C50" s="3">
+        <v>42220</v>
+      </c>
+      <c r="D50" s="3">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C51" s="3">
+        <v>42936</v>
+      </c>
+      <c r="D51" s="3">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="3">
+        <v>40519</v>
+      </c>
+      <c r="D52" s="3">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C53" s="3">
+        <v>42841</v>
+      </c>
+      <c r="D53" s="3">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C54" s="3">
+        <v>42995</v>
+      </c>
+      <c r="D54" s="3">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C55" s="3">
+        <v>44243</v>
+      </c>
+      <c r="D55" s="3">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C56" s="3">
+        <v>42144</v>
+      </c>
+      <c r="D56" s="3">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="3">
+        <v>42359</v>
+      </c>
+      <c r="D57" s="3">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C58" s="3">
+        <v>42864</v>
+      </c>
+      <c r="D58" s="3">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C59" s="3">
+        <v>42856</v>
+      </c>
+      <c r="D59" s="3">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C60" s="3">
+        <v>40870</v>
+      </c>
+      <c r="D60" s="3">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C61" s="3">
+        <v>42088</v>
+      </c>
+      <c r="D61" s="3">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C62" s="3">
+        <v>40804</v>
+      </c>
+      <c r="D62" s="3">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C63" s="3">
+        <v>40673</v>
+      </c>
+      <c r="D63" s="3">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C64" s="3">
+        <v>40822</v>
+      </c>
+      <c r="D64" s="3">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C65" s="3">
+        <v>43233</v>
+      </c>
+      <c r="D65" s="3">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C66" s="3">
+        <v>40717</v>
+      </c>
+      <c r="D66" s="3">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C67" s="3">
+        <v>42911</v>
+      </c>
+      <c r="D67" s="3">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C68" s="3">
+        <v>42462</v>
+      </c>
+      <c r="D68" s="3">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C69" s="3">
+        <v>44033</v>
+      </c>
+      <c r="D69" s="3">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C70" s="3">
+        <v>44199</v>
+      </c>
+      <c r="D70" s="3">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C71" s="3">
+        <v>40429</v>
+      </c>
+      <c r="D71" s="3">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C72" s="3">
+        <v>43912</v>
+      </c>
+      <c r="D72" s="3">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C73" s="3">
+        <v>42615</v>
+      </c>
+      <c r="D73" s="3">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C74" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D74" s="3">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C75" s="3">
+        <v>43290</v>
+      </c>
+      <c r="D75" s="3">
+        <v>33869</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C76" s="3">
+        <v>42402</v>
+      </c>
+      <c r="D76" s="3">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C77" s="3">
+        <v>40635</v>
+      </c>
+      <c r="D77" s="3">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C78" s="3">
+        <v>40838</v>
+      </c>
+      <c r="D78" s="3">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C79" s="3">
+        <v>42072</v>
+      </c>
+      <c r="D79" s="3">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C80" s="3">
+        <v>43358</v>
+      </c>
+      <c r="D80" s="3">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C81" s="3">
+        <v>42593</v>
+      </c>
+      <c r="D81" s="3">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C82" s="3">
+        <v>40667</v>
+      </c>
+      <c r="D82" s="3">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C83" s="3">
+        <v>43624</v>
+      </c>
+      <c r="D83" s="3">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C84" s="3">
+        <v>43053</v>
+      </c>
+      <c r="D84" s="3">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="3">
+        <v>42049</v>
+      </c>
+      <c r="D85" s="3">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C86" s="3">
+        <v>43218</v>
+      </c>
+      <c r="D86" s="3">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C87" s="3">
+        <v>42496</v>
+      </c>
+      <c r="D87" s="3">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C88" s="3">
+        <v>44235</v>
+      </c>
+      <c r="D88" s="3">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C89" s="3">
+        <v>40414</v>
+      </c>
+      <c r="D89" s="3">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C90" s="3">
+        <v>42690</v>
+      </c>
+      <c r="D90" s="3">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C91" s="3">
+        <v>40840</v>
+      </c>
+      <c r="D91" s="3">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C92" s="3">
+        <v>40880</v>
+      </c>
+      <c r="D92" s="3">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C93" s="3">
+        <v>43582</v>
+      </c>
+      <c r="D93" s="3">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C94" s="3">
+        <v>43034</v>
+      </c>
+      <c r="D94" s="3">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C95" s="3">
+        <v>44162</v>
+      </c>
+      <c r="D95" s="3">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C96" s="3">
+        <v>42430</v>
+      </c>
+      <c r="D96" s="3">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C97" s="3">
+        <v>43174</v>
+      </c>
+      <c r="D97" s="3">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="3">
+        <v>42726</v>
+      </c>
+      <c r="D98" s="3">
+        <v>30603</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:D98" xr:uid="{FBAB6909-D6CC-4093-BBDE-750475E501C7}">
+    <sortState ref="A3:D98">
+      <sortCondition ref="A2:A98"/>
+    </sortState>
+  </autoFilter>
+  <conditionalFormatting sqref="A3:D98">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>AND($A3=$G$3,AND($D3&gt;=$H$3,$D3&lt;=$I$3))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816E7EB5-95E2-4C71-8401-74A658B5D609}">
   <dimension ref="E1:J16"/>
@@ -1662,7 +6142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A09AB320-D50B-41B3-91DB-B379FBB4147B}">
-  <dimension ref="E4:L16"/>
+  <dimension ref="E4:L37"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
@@ -1849,9 +6329,45 @@
         <v>8000</v>
       </c>
     </row>
+    <row r="26" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G26" s="3"/>
+    </row>
+    <row r="27" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G27" s="3"/>
+    </row>
+    <row r="28" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G28" s="3"/>
+    </row>
+    <row r="29" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G29" s="3"/>
+    </row>
+    <row r="30" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G30" s="3"/>
+    </row>
+    <row r="31" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G31" s="3"/>
+    </row>
+    <row r="32" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G32" s="3"/>
+    </row>
+    <row r="33" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G33" s="3"/>
+    </row>
+    <row r="34" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G34" s="3"/>
+    </row>
+    <row r="35" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G35" s="3"/>
+    </row>
+    <row r="36" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G36" s="3"/>
+    </row>
+    <row r="37" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G37" s="3"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="F5:F16">
-    <cfRule type="dataBar" priority="2">
+    <cfRule type="dataBar" priority="3">
       <dataBar>
         <cfvo type="min"/>
         <cfvo type="max"/>
@@ -1865,6 +6381,20 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G5:G16">
+    <cfRule type="dataBar" priority="2">
+      <dataBar>
+        <cfvo type="min"/>
+        <cfvo type="max"/>
+        <color rgb="FFFF555A"/>
+      </dataBar>
+      <extLst>
+        <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
+          <x14:id>{2174B4EF-F9FF-4F41-A4C0-686435C2BFB6}</x14:id>
+        </ext>
+      </extLst>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G26:G37">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="min"/>
@@ -1873,7 +6403,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2174B4EF-F9FF-4F41-A4C0-686435C2BFB6}</x14:id>
+          <x14:id>{0A374BE7-A199-447A-A85B-86310164FE25}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -1906,6 +6436,17 @@
             </x14:dataBar>
           </x14:cfRule>
           <xm:sqref>G5:G16</xm:sqref>
+        </x14:conditionalFormatting>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="dataBar" id="{0A374BE7-A199-447A-A85B-86310164FE25}">
+            <x14:dataBar minLength="0" maxLength="100" gradient="0">
+              <x14:cfvo type="autoMin"/>
+              <x14:cfvo type="autoMax"/>
+              <x14:negativeFillColor rgb="FFFF0000"/>
+              <x14:axisColor rgb="FF000000"/>
+            </x14:dataBar>
+          </x14:cfRule>
+          <xm:sqref>G26:G37</xm:sqref>
         </x14:conditionalFormatting>
       </x14:conditionalFormattings>
     </ext>
@@ -2673,22 +7214,22 @@
     <sortCondition ref="F9"/>
   </sortState>
   <conditionalFormatting sqref="G9:G20">
-    <cfRule type="top10" dxfId="10" priority="6" rank="5"/>
+    <cfRule type="top10" dxfId="24" priority="6" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="H9:H20">
-    <cfRule type="top10" dxfId="9" priority="5" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="23" priority="5" bottom="1" rank="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I9:I20">
-    <cfRule type="aboveAverage" dxfId="8" priority="4"/>
+    <cfRule type="aboveAverage" dxfId="22" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J9:J20">
-    <cfRule type="aboveAverage" dxfId="7" priority="3" aboveAverage="0"/>
+    <cfRule type="aboveAverage" dxfId="21" priority="3" aboveAverage="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K9:K20">
-    <cfRule type="top10" dxfId="6" priority="2" percent="1" rank="20"/>
+    <cfRule type="top10" dxfId="20" priority="2" percent="1" rank="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="L9:L20">
-    <cfRule type="top10" dxfId="0" priority="1" percent="1" bottom="1" rank="5"/>
+    <cfRule type="top10" dxfId="19" priority="1" percent="1" bottom="1" rank="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2989,74 +7530,1399 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61830D79-1D6E-43CC-B91F-35DAFBD54708}">
-  <dimension ref="A1:A12"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F92DF25B-34E4-4ACA-A2C9-C1A2A0C027BF}">
+  <dimension ref="A2:H98"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.90625" style="19" customWidth="1"/>
+    <col min="2" max="2" width="25" style="19" customWidth="1"/>
+    <col min="3" max="3" width="16.1796875" style="4" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" style="4" customWidth="1"/>
+    <col min="5" max="6" width="8.7265625" style="4"/>
+    <col min="7" max="7" width="17.81640625" style="4" customWidth="1"/>
+    <col min="8" max="16384" width="8.7265625" style="4"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A1">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" s="17" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="B2" s="17" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="C2" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>83</v>
+      </c>
+      <c r="C3" s="3">
+        <v>43290</v>
+      </c>
+      <c r="D3" s="3">
+        <v>33869</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="C4" s="3">
+        <v>43125</v>
+      </c>
+      <c r="D4" s="3">
+        <v>32686</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="3">
+        <v>40311</v>
+      </c>
+      <c r="D5" s="3">
+        <v>45824</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="3">
+        <v>42777</v>
+      </c>
+      <c r="D6" s="3">
+        <v>19187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="3">
+        <v>42402</v>
+      </c>
+      <c r="D7" s="3">
+        <v>38592</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A8" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="C8" s="3">
+        <v>44168</v>
+      </c>
+      <c r="D8" s="3">
+        <v>35035</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A9" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="18" t="s">
+        <v>91</v>
+      </c>
+      <c r="C9" s="3">
+        <v>43371</v>
+      </c>
+      <c r="D9" s="3">
+        <v>15650</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A10" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B10" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="3">
+        <v>40673</v>
+      </c>
+      <c r="D10" s="3">
+        <v>23117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A11" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B11" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="C11" s="3">
+        <v>43403</v>
+      </c>
+      <c r="D11" s="3">
+        <v>32039</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A12" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B12" s="18" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="3">
+        <v>40822</v>
+      </c>
+      <c r="D12" s="3">
+        <v>38562</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A13" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>96</v>
+      </c>
+      <c r="C13" s="3">
+        <v>43678</v>
+      </c>
+      <c r="D13" s="3">
+        <v>43948</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A14" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B14" s="18" t="s">
+        <v>97</v>
+      </c>
+      <c r="C14" s="3">
+        <v>43623</v>
+      </c>
+      <c r="D14" s="3">
+        <v>27580</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A15" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>98</v>
+      </c>
+      <c r="C15" s="3">
+        <v>43233</v>
+      </c>
+      <c r="D15" s="3">
+        <v>19377</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A16" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="C16" s="3">
+        <v>40717</v>
+      </c>
+      <c r="D16" s="3">
+        <v>26799</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" s="18" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="C17" s="3">
+        <v>40397</v>
+      </c>
+      <c r="D17" s="3">
+        <v>40037</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B18" s="18" t="s">
+        <v>101</v>
+      </c>
+      <c r="C18" s="3">
+        <v>40635</v>
+      </c>
+      <c r="D18" s="3">
+        <v>40052</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="3">
+        <v>42970</v>
+      </c>
+      <c r="D19" s="3">
+        <v>21921</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B20" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="C20" s="3">
+        <v>40838</v>
+      </c>
+      <c r="D20" s="3">
+        <v>39053</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>104</v>
+      </c>
+      <c r="C21" s="3">
+        <v>42496</v>
+      </c>
+      <c r="D21" s="3">
+        <v>21349</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>105</v>
+      </c>
+      <c r="C22" s="3">
+        <v>42072</v>
+      </c>
+      <c r="D22" s="3">
+        <v>36815</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>106</v>
+      </c>
+      <c r="C23" s="3">
+        <v>42272</v>
+      </c>
+      <c r="D23" s="3">
+        <v>32797</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="18" t="s">
+        <v>107</v>
+      </c>
+      <c r="C24" s="3">
+        <v>44139</v>
+      </c>
+      <c r="D24" s="3">
+        <v>48767</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="3">
+        <v>43358</v>
+      </c>
+      <c r="D25" s="3">
+        <v>49942</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B26" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C26" s="3">
+        <v>42911</v>
+      </c>
+      <c r="D26" s="3">
+        <v>17302</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" s="18" t="s">
         <v>110</v>
       </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="C27" s="3">
+        <v>44235</v>
+      </c>
+      <c r="D27" s="3">
+        <v>33234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B28" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="C28" s="3">
+        <v>42462</v>
+      </c>
+      <c r="D28" s="3">
+        <v>25893</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="3">
+        <v>43129</v>
+      </c>
+      <c r="D29" s="3">
+        <v>18200</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B30" s="18" t="s">
+        <v>113</v>
+      </c>
+      <c r="C30" s="3">
+        <v>44033</v>
+      </c>
+      <c r="D30" s="3">
+        <v>24185</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>114</v>
+      </c>
+      <c r="C31" s="3">
+        <v>43442</v>
+      </c>
+      <c r="D31" s="3">
+        <v>30209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B32" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C32" s="3">
+        <v>43447</v>
+      </c>
+      <c r="D32" s="3">
+        <v>31623</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C33" s="3">
+        <v>43980</v>
+      </c>
+      <c r="D33" s="3">
+        <v>18072</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B34" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="C34" s="3">
+        <v>42593</v>
+      </c>
+      <c r="D34" s="3">
+        <v>15187</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35" s="18" t="s">
+        <v>118</v>
+      </c>
+      <c r="C35" s="3">
+        <v>43216</v>
+      </c>
+      <c r="D35" s="3">
+        <v>11793</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B36" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C36" s="3">
+        <v>44199</v>
+      </c>
+      <c r="D36" s="3">
+        <v>13505</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>120</v>
       </c>
+      <c r="C37" s="3">
+        <v>40837</v>
+      </c>
+      <c r="D37" s="3">
+        <v>25396</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B38" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="C38" s="3">
+        <v>42914</v>
+      </c>
+      <c r="D38" s="3">
+        <v>21884</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B39" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C39" s="3">
+        <v>40429</v>
+      </c>
+      <c r="D39" s="3">
+        <v>10484</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B40" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="C40" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D40" s="3">
+        <v>18613</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="C41" s="3">
+        <v>43160</v>
+      </c>
+      <c r="D41" s="3">
+        <v>12367</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A42" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B42" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C42" s="3">
+        <v>40667</v>
+      </c>
+      <c r="D42" s="3">
+        <v>36754</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A43" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="3">
+        <v>42813</v>
+      </c>
+      <c r="D43" s="3">
+        <v>43035</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A44" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B44" s="18" t="s">
+        <v>128</v>
+      </c>
+      <c r="C44" s="3">
+        <v>43624</v>
+      </c>
+      <c r="D44" s="3">
+        <v>11787</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A45" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" s="18" t="s">
+        <v>129</v>
+      </c>
+      <c r="C45" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D45" s="3">
+        <v>43719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A46" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="18" t="s">
+        <v>130</v>
+      </c>
+      <c r="C46" s="3">
+        <v>43912</v>
+      </c>
+      <c r="D46" s="3">
+        <v>17272</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A47" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B47" s="18" t="s">
+        <v>131</v>
+      </c>
+      <c r="C47" s="3">
+        <v>43053</v>
+      </c>
+      <c r="D47" s="3">
+        <v>16726</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A48" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="18" t="s">
+        <v>132</v>
+      </c>
+      <c r="C48" s="3">
+        <v>42615</v>
+      </c>
+      <c r="D48" s="3">
+        <v>46904</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A49" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B49" s="18" t="s">
+        <v>133</v>
+      </c>
+      <c r="C49" s="3">
+        <v>40414</v>
+      </c>
+      <c r="D49" s="3">
+        <v>23543</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A50" s="18" t="s">
+        <v>92</v>
+      </c>
+      <c r="B50" s="18" t="s">
+        <v>134</v>
+      </c>
+      <c r="C50" s="3">
+        <v>44169</v>
+      </c>
+      <c r="D50" s="3">
+        <v>10251</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A51" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B51" s="18" t="s">
+        <v>135</v>
+      </c>
+      <c r="C51" s="3">
+        <v>44142</v>
+      </c>
+      <c r="D51" s="3">
+        <v>39163</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A52" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" s="18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C52" s="3">
+        <v>42067</v>
+      </c>
+      <c r="D52" s="3">
+        <v>41330</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A53" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B53" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="C53" s="3">
+        <v>42378</v>
+      </c>
+      <c r="D53" s="3">
+        <v>49266</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B54" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="C54" s="3">
+        <v>40556</v>
+      </c>
+      <c r="D54" s="3">
+        <v>33138</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A55" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" s="18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C55" s="3">
+        <v>42954</v>
+      </c>
+      <c r="D55" s="3">
+        <v>39896</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A56" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B56" s="18" t="s">
+        <v>140</v>
+      </c>
+      <c r="C56" s="3">
+        <v>42129</v>
+      </c>
+      <c r="D56" s="3">
+        <v>26816</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B57" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="C57" s="3">
+        <v>42220</v>
+      </c>
+      <c r="D57" s="3">
+        <v>30642</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C58" s="3">
+        <v>42477</v>
+      </c>
+      <c r="D58" s="3">
+        <v>10356</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B59" s="18" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="3">
+        <v>44382</v>
+      </c>
+      <c r="D59" s="3">
+        <v>30172</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A60" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B60" s="18" t="s">
+        <v>144</v>
+      </c>
+      <c r="C60" s="3">
+        <v>42936</v>
+      </c>
+      <c r="D60" s="3">
+        <v>20638</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B61" s="18" t="s">
+        <v>145</v>
+      </c>
+      <c r="C61" s="3">
+        <v>40519</v>
+      </c>
+      <c r="D61" s="3">
+        <v>48723</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B62" s="18" t="s">
+        <v>146</v>
+      </c>
+      <c r="C62" s="3">
+        <v>42841</v>
+      </c>
+      <c r="D62" s="3">
+        <v>33001</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B63" s="18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" s="3">
+        <v>42995</v>
+      </c>
+      <c r="D63" s="3">
+        <v>19399</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B64" s="18" t="s">
+        <v>148</v>
+      </c>
+      <c r="C64" s="3">
+        <v>44243</v>
+      </c>
+      <c r="D64" s="3">
+        <v>49110</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A65" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B65" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="C65" s="3">
+        <v>42144</v>
+      </c>
+      <c r="D65" s="3">
+        <v>23343</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A66" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" s="18" t="s">
+        <v>150</v>
+      </c>
+      <c r="C66" s="3">
+        <v>42296</v>
+      </c>
+      <c r="D66" s="3">
+        <v>19655</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A67" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" s="3">
+        <v>40898</v>
+      </c>
+      <c r="D67" s="3">
+        <v>47333</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B68" s="18" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="3">
+        <v>43791</v>
+      </c>
+      <c r="D68" s="3">
+        <v>22923</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B69" s="18" t="s">
+        <v>153</v>
+      </c>
+      <c r="C69" s="3">
+        <v>44131</v>
+      </c>
+      <c r="D69" s="3">
+        <v>35928</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="C70" s="3">
+        <v>42428</v>
+      </c>
+      <c r="D70" s="3">
+        <v>41138</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>155</v>
+      </c>
+      <c r="C71" s="3">
+        <v>42690</v>
+      </c>
+      <c r="D71" s="3">
+        <v>18320</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>156</v>
+      </c>
+      <c r="C72" s="3">
+        <v>42359</v>
+      </c>
+      <c r="D72" s="3">
+        <v>27784</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C73" s="3">
+        <v>40840</v>
+      </c>
+      <c r="D73" s="3">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="C74" s="3">
+        <v>40880</v>
+      </c>
+      <c r="D74" s="3">
+        <v>42096</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="C75" s="3">
+        <v>42049</v>
+      </c>
+      <c r="D75" s="3">
+        <v>37535</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="C76" s="3">
+        <v>43582</v>
+      </c>
+      <c r="D76" s="3">
+        <v>41644</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>161</v>
+      </c>
+      <c r="C77" s="3">
+        <v>43034</v>
+      </c>
+      <c r="D77" s="3">
+        <v>34897</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>162</v>
+      </c>
+      <c r="C78" s="3">
+        <v>43060</v>
+      </c>
+      <c r="D78" s="3">
+        <v>44778</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C79" s="3">
+        <v>43846</v>
+      </c>
+      <c r="D79" s="3">
+        <v>16799</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="C80" s="3">
+        <v>44162</v>
+      </c>
+      <c r="D80" s="3">
+        <v>32527</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A81" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="C81" s="3">
+        <v>43788</v>
+      </c>
+      <c r="D81" s="3">
+        <v>14965</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A82" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="C82" s="3">
+        <v>42864</v>
+      </c>
+      <c r="D82" s="3">
+        <v>10953</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A83" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" s="18" t="s">
+        <v>167</v>
+      </c>
+      <c r="C83" s="3">
+        <v>42856</v>
+      </c>
+      <c r="D83" s="3">
+        <v>30092</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B84" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C84" s="3">
+        <v>44122</v>
+      </c>
+      <c r="D84" s="3">
+        <v>17520</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B85" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="C85" s="3">
+        <v>40901</v>
+      </c>
+      <c r="D85" s="3">
+        <v>32384</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="C86" s="3">
+        <v>42430</v>
+      </c>
+      <c r="D86" s="3">
+        <v>38127</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A87" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="C87" s="3">
+        <v>43017</v>
+      </c>
+      <c r="D87" s="3">
+        <v>46585</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A88" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B88" s="18" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" s="3">
+        <v>43174</v>
+      </c>
+      <c r="D88" s="3">
+        <v>35407</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A89" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B89" s="18" t="s">
+        <v>173</v>
+      </c>
+      <c r="C89" s="3">
+        <v>43951</v>
+      </c>
+      <c r="D89" s="3">
+        <v>31003</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A90" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" s="18" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" s="3">
+        <v>40870</v>
+      </c>
+      <c r="D90" s="3">
+        <v>49204</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A91" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>175</v>
+      </c>
+      <c r="C91" s="3">
+        <v>42726</v>
+      </c>
+      <c r="D91" s="3">
+        <v>30603</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A92" s="18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B92" s="18" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="3">
+        <v>44229</v>
+      </c>
+      <c r="D92" s="3">
+        <v>47275</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A93" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="18" t="s">
+        <v>177</v>
+      </c>
+      <c r="C93" s="3">
+        <v>42088</v>
+      </c>
+      <c r="D93" s="3">
+        <v>43721</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A94" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C94" s="3">
+        <v>43218</v>
+      </c>
+      <c r="D94" s="3">
+        <v>13577</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A95" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B95" s="18" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="3">
+        <v>40804</v>
+      </c>
+      <c r="D95" s="3">
+        <v>27449</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A96" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B96" s="18" t="s">
+        <v>180</v>
+      </c>
+      <c r="C96" s="3">
+        <v>43609</v>
+      </c>
+      <c r="D96" s="3">
+        <v>47391</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A97" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="B97" s="18" t="s">
+        <v>181</v>
+      </c>
+      <c r="C97" s="3">
+        <v>40469</v>
+      </c>
+      <c r="D97" s="3">
+        <v>47001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A98" s="18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B98" s="18" t="s">
+        <v>182</v>
+      </c>
+      <c r="C98" s="3">
+        <v>44179</v>
+      </c>
+      <c r="D98" s="3">
+        <v>30335</v>
+      </c>
     </row>
   </sheetData>
-  <sortState ref="A1:A12">
-    <sortCondition ref="A1"/>
-  </sortState>
+  <autoFilter ref="A2:D98" xr:uid="{00E6E89A-8580-41A2-802A-D3ACDA8E2666}"/>
+  <conditionalFormatting sqref="G3">
+    <cfRule type="expression" dxfId="18" priority="2">
+      <formula>$A3=$G$3</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A3:D98">
+    <cfRule type="expression" dxfId="17" priority="1">
+      <formula>$A3=$G$3</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>